--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/CONNECTICUT_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/CONNECTICUT_2020.xlsx
@@ -823,7 +823,7 @@
         <v>16</v>
       </c>
       <c r="D26">
-        <v>0.009925558312655087</v>
+        <v>0.009925558312655089</v>
       </c>
     </row>
     <row r="27">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C66">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C110">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C218">
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C305">
